--- a/sources/jack2_step1.xlsx
+++ b/sources/jack2_step1.xlsx
@@ -2717,9 +2717,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
-        <f>~3+4</f>
-        <v/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5568,9 +5569,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <f>~3+4</f>
-        <v/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
